--- a/bindings/excel/examples/workbooks/historical_pricing_example.xlsx
+++ b/bindings/excel/examples/workbooks/historical_pricing_example.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6018bc907cdb526/Escritorio/Pega/quantsupport/bindings/excel/examples/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_1A3A94A9C4225A4E5E64B80B9C6D405C84C9961E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84BBB7B8-8F44-4502-8185-FE2920B93E74}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -21,7 +15,6 @@
     <sheet name="5 Results" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Start Here'!$A$1:$F$28</definedName>
     <definedName name="History_ActualDate1">'5 Results'!$B$9</definedName>
     <definedName name="History_ActualDate2">'5 Results'!$C$9</definedName>
     <definedName name="History_Archive">'3 Archive'!$B$35</definedName>
@@ -66,36 +59,24 @@
     <definedName name="History_Timestamp2">'2 Markets'!$C$8</definedName>
     <definedName name="History_Trade">'4 Pricing'!$B$10</definedName>
     <definedName name="History_TradeDate">'1 Inputs'!$B$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Start Here'!$A$1:$F$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1 Inputs'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2 Markets'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'3 Archive'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'4 Pricing'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'5 Results'!$1:$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -108,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="B8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -121,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="B9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -134,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -147,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
+    <comment ref="B11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -160,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
+    <comment ref="B12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -178,12 +159,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -196,7 +177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -209,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -222,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -235,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -248,7 +229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
+    <comment ref="B22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -261,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+    <comment ref="B25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -274,7 +255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
+    <comment ref="B28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -287,7 +268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
+    <comment ref="B35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -305,12 +286,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -323,7 +304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -336,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -349,7 +330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -362,7 +343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -375,7 +356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
+    <comment ref="B22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -388,7 +369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
+    <comment ref="B25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -401,7 +382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+    <comment ref="B28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -414,7 +395,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
+    <comment ref="B31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -427,7 +408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000A000000}">
+    <comment ref="B34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -862,11 +843,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1040,9 +1023,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1066,47 +1055,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,84 +1073,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/volatileDependencies.xml><?xml version="1.0" encoding="utf-8"?>
-<volTypes xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <volType type="realTimeData">
-    <main first="rtdsrv_55237fef61064219bfde5241478f83c5">
-      <tp>
-        <v>4</v>
-        <stp/>
-        <stp>888f65bc-56c9-4815-89a1-1955c9a18652</stp>
-        <tr r="C12" s="6"/>
-      </tp>
-      <tp>
-        <v>14</v>
-        <stp/>
-        <stp>e561c94f-a363-4fc9-968b-6641c518b67d</stp>
-        <tr r="B34" s="5"/>
-      </tp>
-      <tp>
-        <v>16</v>
-        <stp/>
-        <stp>0b12a9a5-640d-4337-b250-5b55fa1814df</stp>
-        <tr r="B28" s="4"/>
-      </tp>
-      <tp>
-        <v>16</v>
-        <stp/>
-        <stp>1ad0fe92-5989-4f69-b195-da9e01289263</stp>
-        <tr r="B12" s="6"/>
-      </tp>
-      <tp>
-        <v>16</v>
-        <stp/>
-        <stp>2c44b509-9c59-491b-8945-38cd11766a6b</stp>
-        <tr r="B35" s="4"/>
-      </tp>
-      <tp>
-        <v>15</v>
-        <stp/>
-        <stp>f02bc5fd-94c3-41c6-aed5-0ddf85ccc260</stp>
-        <tr r="B22" s="5"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>8cafa83d-7b25-4475-b6f4-739b78c018ed</stp>
-        <tr r="B25" s="5"/>
-      </tp>
-      <tp>
-        <v>15</v>
-        <stp/>
-        <stp>cf3523ec-b287-4e71-a229-3b3e0524dd9e</stp>
-        <tr r="B31" s="5"/>
-      </tp>
-      <tp>
-        <v>16</v>
-        <stp/>
-        <stp>03a83eaf-3284-45dc-b6e9-2b3a56933274</stp>
-        <tr r="B16" s="4"/>
-      </tp>
-    </main>
-  </volType>
-</volTypes>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1229,7 +1117,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1263,7 +1151,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1298,10 +1185,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1474,12 +1360,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="26.1" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="26.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
@@ -1488,243 +1374,243 @@
     <col min="6" max="6" width="18.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" ht="30" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-    </row>
-    <row r="4" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-    </row>
-    <row r="6" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="6" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-    </row>
-    <row r="7" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-    </row>
-    <row r="9" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-    </row>
-    <row r="10" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="14" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-    </row>
-    <row r="11" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-    </row>
-    <row r="12" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="14" t="s">
+      <c r="C12" s="7"/>
+      <c r="D12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-    </row>
-    <row r="13" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="14" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="17" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="17" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1">
+      <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="14" t="s">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-    </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="30" customHeight="1">
+      <c r="A19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="14" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1">
+      <c r="A20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="14" t="s">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-    </row>
-    <row r="22" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="22" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-    </row>
-    <row r="23" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-    </row>
-    <row r="24" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-    </row>
-    <row r="25" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-    </row>
-    <row r="27" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="27" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A27" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-    </row>
-    <row r="28" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -1745,22 +1631,22 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A27:F28"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A27:F28"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B10" location="'1 Inputs'!A1" display="1 Inputs" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B11" location="'2 Markets'!A1" display="2 Markets" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B12" location="'3 Archive'!A1" display="3 Archive" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B13" location="'4 Pricing'!A1" display="4 Pricing" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B14" location="'5 Results'!A1" display="5 Results" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B10" location="'1 Inputs'!A1" display="1 Inputs"/>
+    <hyperlink ref="B11" location="'2 Markets'!A1" display="2 Markets"/>
+    <hyperlink ref="B12" location="'3 Archive'!A1" display="3 Archive"/>
+    <hyperlink ref="B13" location="'4 Pricing'!A1" display="4 Pricing"/>
+    <hyperlink ref="B14" location="'5 Results'!A1" display="5 Results"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -1768,172 +1654,172 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF337AB7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="62.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="32.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="32.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="32.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="32.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="11">
         <v>1000000</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="32.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="12">
         <v>0.04</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="32.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:3" ht="36" customHeight="1">
+      <c r="A16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="24" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="24" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:3" ht="24" customHeight="1">
+      <c r="A21" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-    </row>
-    <row r="22" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-    </row>
-    <row r="23" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+    </row>
+    <row r="22" spans="1:3" ht="24" customHeight="1">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+    </row>
+    <row r="23" spans="1:3" ht="24" customHeight="1">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1941,14 +1827,17 @@
     <mergeCell ref="A2:C3"/>
     <mergeCell ref="A21:C23"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C18" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17">
+      <formula1>"Exact,Previous,Closest"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18">
       <formula1>"Exact,Previous,Closest"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="C4" location="'2 Markets'!A1" display="Next → 2 Markets" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="C4" location="'2 Markets'!A1" display="Next → 2 Markets"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -1960,120 +1849,120 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF337AB7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
     <col min="2" max="3" width="30.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="24" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="24" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:3" ht="36" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:3" ht="24" customHeight="1">
+      <c r="A12" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="12">
         <v>0.04</v>
       </c>
-      <c r="C12" s="10">
-        <v>4.1000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="C12" s="12">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="24" customHeight="1">
+      <c r="A13" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="10">
-        <v>3.9E-2</v>
-      </c>
-      <c r="C13" s="10">
+      <c r="B13" s="12">
+        <v>0.039</v>
+      </c>
+      <c r="C13" s="12">
         <v>0.04</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:3" ht="24" customHeight="1">
+      <c r="A14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="10">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="C14" s="10">
-        <v>3.9E-2</v>
+      <c r="B14" s="12">
+        <v>0.038</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0.039</v>
       </c>
     </row>
   </sheetData>
@@ -2082,8 +1971,8 @@
     <mergeCell ref="A2:C3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="C4" location="'3 Archive'!A1" display="Next → 3 Archive" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="C4" location="'3 Archive'!A1" display="Next → 3 Archive"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -2094,270 +1983,270 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="8" t="str" cm="1">
+      <c r="B7" s="10" cm="1" t="str">
         <f t="array" ref="B7">_xll.QS.CONTEXT.CREATE("History.Root1",History_Date1,"USD","SOFR")</f>
-        <v>QSObject:PricingContext:w1~History.Root1:2</v>
-      </c>
-      <c r="C7" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
-        <v>=QS.CONTEXT.CREATE("History.Root1";History_Date1;"USD";"SOFR")</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-    </row>
-    <row r="10" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="8" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A8" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
+        <v>=QS.CONTEXT.CREATE("History.Root1", History_Date1, "USD", "SOFR")</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+    </row>
+    <row r="10" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="8" t="str" cm="1">
+      <c r="B10" s="10" cm="1" t="str">
         <f t="array" ref="B10">_xll.QS.CONTEXT.ADD.ZERO.CURVE(History_Root1,"SOFR",History_Pillars,History_Rates1,"Actual365","Continuous","Annual","Linear",FALSE)</f>
-        <v>QSObject:ContextInput:w1~context.input.e1513b702e645741.1286304496544.9.1:3</v>
-      </c>
-      <c r="C10" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
-        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root1;"SOFR";History_Pillars;History_Rates1;"Actual365";"Continuous";"Annual";"Linear";FALSO)</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-    </row>
-    <row r="13" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="11" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A11" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root1, "SOFR", History_Pillars, History_Rates1, "Actual365", "Continuous", "Annual", "Linear", FALSE)</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+    </row>
+    <row r="13" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="8" t="str" cm="1">
-        <f t="array" ref="B13">History_Root1</f>
-        <v>QSObject:PricingContext:w1~History.Root1:2</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="10">
+        <f>History_Root1</f>
+        <v/>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
+    <row r="14" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A14" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
         <v>=History_Root1</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-    </row>
-    <row r="16" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+    </row>
+    <row r="16" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="8" t="str" cm="1">
+      <c r="B16" s="10" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot1",History_Timestamp1,History_OriginalContext1)</f>
-        <v>QSEngine:1:24</v>
-      </c>
-      <c r="C16" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
-        <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot1";History_Timestamp1;History_OriginalContext1)</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-    </row>
-    <row r="19" spans="1:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="17" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A17" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
+        <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot1", History_Timestamp1, History_OriginalContext1)</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+    </row>
+    <row r="19" spans="1:4" ht="38.25" customHeight="1">
+      <c r="A19" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="8" t="str" cm="1">
+      <c r="B19" s="10" cm="1" t="str">
         <f t="array" ref="B19">_xll.QS.CONTEXT.CREATE("History.Root2",History_Date2,"USD","SOFR")</f>
-        <v>QSObject:PricingContext:w1~History.Root2:1</v>
-      </c>
-      <c r="C19" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
-        <v>=QS.CONTEXT.CREATE("History.Root2";History_Date2;"USD";"SOFR")</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-    </row>
-    <row r="22" spans="1:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="20" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A20" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
+        <v>=QS.CONTEXT.CREATE("History.Root2", History_Date2, "USD", "SOFR")</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+    </row>
+    <row r="22" spans="1:4" ht="38.25" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="8" t="str" cm="1">
+      <c r="B22" s="10" cm="1" t="str">
         <f t="array" ref="B22">_xll.QS.CONTEXT.ADD.ZERO.CURVE(History_Root2,"SOFR",History_Pillars,History_Rates2,"Actual365","Continuous","Annual","Linear",FALSE)</f>
-        <v>QSObject:ContextInput:w1~context.input.dba204d9994e78bc.1286304496544.21.1:4</v>
-      </c>
-      <c r="C22" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
-        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root2;"SOFR";History_Pillars;History_Rates2;"Actual365";"Continuous";"Annual";"Linear";FALSO)</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-    </row>
-    <row r="25" spans="1:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="23" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A23" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root2, "SOFR", History_Pillars, History_Rates2, "Actual365", "Continuous", "Annual", "Linear", FALSE)</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+    </row>
+    <row r="25" spans="1:4" ht="38.25" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="8" t="str" cm="1">
-        <f t="array" ref="B25">History_Root2</f>
-        <v>QSObject:PricingContext:w1~History.Root2:1</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="10">
+        <f>History_Root2</f>
+        <v/>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
+    <row r="26" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A26" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
         <v>=History_Root2</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-    </row>
-    <row r="28" spans="1:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+    </row>
+    <row r="28" spans="1:4" ht="38.25" customHeight="1">
+      <c r="A28" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="8" t="str" cm="1">
+      <c r="B28" s="10" cm="1" t="str">
         <f t="array" ref="B28">_xll.QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot2",History_Timestamp2,History_OriginalContext2)</f>
-        <v>QSEngine:1:26</v>
-      </c>
-      <c r="C28" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
-        <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot2";History_Timestamp2;History_OriginalContext2)</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-    </row>
-    <row r="31" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+    <row r="29" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A29" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
+        <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot2", History_Timestamp2, History_OriginalContext2)</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+    </row>
+    <row r="31" spans="1:4" ht="36" customHeight="1">
+      <c r="A31" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" ht="24" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="8" t="str">
+      <c r="B32" s="10">
         <f>History_OriginalContext1</f>
-        <v>QSObject:PricingContext:w1~History.Root1:2</v>
-      </c>
-      <c r="D32" s="6" t="str">
+        <v/>
+      </c>
+      <c r="D32" s="8">
         <f>History_Timestamp1</f>
-        <v>2026-01-15T16:00:00Z</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="24" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B33" s="8" t="str">
+      <c r="B33" s="10">
         <f>History_OriginalContext2</f>
-        <v>QSObject:PricingContext:w1~History.Root2:1</v>
-      </c>
-      <c r="D33" s="6" t="str">
+        <v/>
+      </c>
+      <c r="D33" s="8">
         <f>History_Timestamp2</f>
-        <v>2026-01-16T16:00:00Z</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="38.25" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="8" t="str" cm="1">
+      <c r="B35" s="10" cm="1" t="str">
         <f t="array" ref="B35">_xll.QS.SNAPSHOT.FROM.RANGE("History.Archive",History_Snapshots,History_ObservationTimes)</f>
-        <v>QSEngine:1:25</v>
-      </c>
-      <c r="C35" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B35),",",", ")</f>
-        <v>=QS.SNAPSHOT.FROM.RANGE("History.Archive";History_Snapshots;History_ObservationTimes)</v>
-      </c>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
+    <row r="36" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A36" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B35),",",", ")</f>
+        <v>=QS.SNAPSHOT.FROM.RANGE("History.Archive", History_Snapshots, History_ObservationTimes)</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2366,16 +2255,16 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A36:C36"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A36:C36"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="C4" location="'4 Pricing'!A1" display="Next → 4 Pricing" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="C4" location="'4 Pricing'!A1" display="Next → 4 Pricing"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -2387,255 +2276,255 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="8" t="str" cm="1">
-        <f t="array" ref="B7">_xll.QS.INSTRUMENT.SWAP("History.Instrument",History_Start,History_Maturity,"USD","SOFR",History_Notional,History_FixedRate,0,"Actual360","Simple","Semiannual","Semiannual","Quarterly")</f>
-        <v>QSObject:Swap:w1~History.Instrument:8</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="10" cm="1" t="str">
+        <f t="array" ref="B7">_xll.QS.INSTRUMENT.SWAP("History.Instrument",History_OriginalContext1,History_Start,History_Maturity,"USD","SOFR",History_Notional,History_FixedRate,0,"Actual360","Simple","Semiannual","Semiannual","Quarterly")</f>
+        <v/>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
-        <v>=QS.INSTRUMENT.SWAP("History.Instrument";History_Start;History_Maturity;"USD";"SOFR";History_Notional;History_FixedRate;0;"Actual360";"Simple";"Semiannual";"Semiannual";"Quarterly")</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-    </row>
-    <row r="10" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="8" spans="1:3" ht="48" customHeight="1">
+      <c r="A8" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
+        <v>=QS.INSTRUMENT.SWAP("History.Instrument", History_OriginalContext1, History_Start, History_Maturity, "USD", "SOFR", History_Notional, History_FixedRate, 0, "Actual360", "Simple", "Semiannual", "Semiannual", "Quarterly")</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+    </row>
+    <row r="10" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="8" t="str" cm="1">
-        <f t="array" ref="B10">_xll.QS.TRADE.CREATE("History.Trade",History_Instrument,History_TradeDate,History_Side)</f>
-        <v>QSObject:SwapTrade:w1~History.Trade:10</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="10" cm="1" t="str">
+        <f t="array" ref="B10">_xll.QS.TRADE.CREATE("History.Trade",History_OriginalContext1,History_Instrument,History_TradeDate,History_Side)</f>
+        <v/>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
-        <v>=QS.TRADE.CREATE("History.Trade";History_Instrument;History_TradeDate;History_Side)</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-    </row>
-    <row r="13" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="11" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A11" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
+        <v>=QS.TRADE.CREATE("History.Trade", History_OriginalContext1, History_Instrument, History_TradeDate, History_Side)</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+    </row>
+    <row r="13" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="8" t="str" cm="1">
+      <c r="B13" s="10" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.DISCOUNT.POLICY.CSA("History.Policy","USD","SOFR")</f>
-        <v>QSObject:SingleCurveCSADiscountPolicy:w1~History.Policy:7</v>
-      </c>
-      <c r="C13" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
-        <v>=QS.DISCOUNT.POLICY.CSA("History.Policy";"USD";"SOFR")</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-    </row>
-    <row r="16" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="14" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A14" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
+        <v>=QS.DISCOUNT.POLICY.CSA("History.Policy", "USD", "SOFR")</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+    </row>
+    <row r="16" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="8" t="str" cm="1">
+      <c r="B16" s="10" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.PRICER.CREATE("History.Pricer","DiscountedCashflowPricer",History_Policy)</f>
-        <v>QSObject:Pricer:w1~History.Pricer:9</v>
-      </c>
-      <c r="C16" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
-        <v>=QS.PRICER.CREATE("History.Pricer";"DiscountedCashflowPricer";History_Policy)</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-    </row>
-    <row r="19" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="17" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A17" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
+        <v>=QS.PRICER.CREATE("History.Pricer", "DiscountedCashflowPricer", History_Policy)</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+    </row>
+    <row r="19" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A19" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="8" t="str" cm="1">
+      <c r="B19" s="10" cm="1" t="str">
         <f t="array" ref="B19">_xll.QS.SNAPSHOT.SELECTOR("History.Selector1",History_Query1,History_Rule1,"Mid")</f>
-        <v>QSObject:SnapshotSelector:w1~History.Selector1:5</v>
-      </c>
-      <c r="C19" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
-        <v>=QS.SNAPSHOT.SELECTOR("History.Selector1";History_Query1;History_Rule1;"Mid")</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-    </row>
-    <row r="22" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="20" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A20" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
+        <v>=QS.SNAPSHOT.SELECTOR("History.Selector1", History_Query1, History_Rule1, "Mid")</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+    </row>
+    <row r="22" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="8" t="e" cm="1">
+      <c r="B22" s="10" cm="1" t="str">
         <f t="array" ref="B22">_xll.QS.CONTEXT.FROM.SNAPSHOT("History.Selected1",History_Archive,History_Selector1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C22" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
-        <v>=QS.CONTEXT.FROM.SNAPSHOT("History.Selected1";History_Archive;History_Selector1)</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-    </row>
-    <row r="25" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="23" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A23" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
+        <v>=QS.CONTEXT.FROM.SNAPSHOT("History.Selected1", History_Archive, History_Selector1)</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+    </row>
+    <row r="25" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="8" t="e" cm="1">
+      <c r="B25" s="10" cm="1" t="str">
         <f t="array" ref="B25">_xll.QS.EVALUATE.RESULTS(History_Context1,History_Trade,"Value",History_Pricer)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
-        <v>=QS.EVALUATE.RESULTS(History_Context1;History_Trade;"Value";History_Pricer)</v>
-      </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-    </row>
-    <row r="28" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+    <row r="26" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A26" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
+        <v>=QS.EVALUATE.RESULTS(History_Context1, History_Trade, "Value", History_Pricer)</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+    </row>
+    <row r="28" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A28" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="8" t="str" cm="1">
+      <c r="B28" s="10" cm="1" t="str">
         <f t="array" ref="B28">_xll.QS.SNAPSHOT.SELECTOR("History.Selector2",History_Query2,History_Rule2,"Mid")</f>
-        <v>QSObject:SnapshotSelector:w1~History.Selector2:6</v>
-      </c>
-      <c r="C28" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
-        <v>=QS.SNAPSHOT.SELECTOR("History.Selector2";History_Query2;History_Rule2;"Mid")</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-    </row>
-    <row r="31" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+    <row r="29" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A29" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
+        <v>=QS.SNAPSHOT.SELECTOR("History.Selector2", History_Query2, History_Rule2, "Mid")</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+    </row>
+    <row r="31" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="8" t="str" cm="1">
+      <c r="B31" s="10" cm="1" t="str">
         <f t="array" ref="B31">_xll.QS.CONTEXT.FROM.SNAPSHOT("History.Selected2",History_Archive,History_Selector2)</f>
-        <v>QSEngine:1:35</v>
-      </c>
-      <c r="C31" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
-        <v>=QS.CONTEXT.FROM.SNAPSHOT("History.Selected2";History_Archive;History_Selector2)</v>
-      </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-    </row>
-    <row r="34" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+    <row r="32" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A32" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
+        <v>=QS.CONTEXT.FROM.SNAPSHOT("History.Selected2", History_Archive, History_Selector2)</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+    </row>
+    <row r="34" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B34" s="8" t="e" cm="1">
+      <c r="B34" s="10" cm="1" t="str">
         <f t="array" ref="B34">_xll.QS.EVALUATE.RESULTS(History_Context2,History_Trade,"Value",History_Pricer)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C34" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B34),",",", ")</f>
-        <v>=QS.EVALUATE.RESULTS(History_Context2;History_Trade;"Value";History_Pricer)</v>
-      </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
+    <row r="35" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A35" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B34),",",", ")</f>
+        <v>=QS.EVALUATE.RESULTS(History_Context2, History_Trade, "Value", History_Pricer)</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2644,17 +2533,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A35:C35"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="C4" location="'5 Results'!A1" display="Next → 5 Results" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="C4" location="'5 Results'!A1" display="Next → 5 Results"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -2666,133 +2555,133 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF21845B"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.7109375" style="1" customWidth="1"/>
     <col min="2" max="3" width="36.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-    </row>
-    <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="24" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="36" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="9">
         <f>History_Query1</f>
-        <v>2026-01-15T16:00:00Z</v>
-      </c>
-      <c r="C7" s="7" t="str">
+        <v/>
+      </c>
+      <c r="C7" s="9">
         <f>History_Query2</f>
-        <v>2026-01-16T16:00:00Z</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="36" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="7" t="e" cm="1">
+      <c r="B8" s="9" cm="1" t="str">
         <f t="array" ref="B8">_xll.QS.CONTEXT.SNAPSHOT.TIMESTAMP(History_Context1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C8" s="7" t="str" cm="1">
+        <v/>
+      </c>
+      <c r="C8" s="9" cm="1" t="str">
         <f t="array" ref="C8">_xll.QS.CONTEXT.SNAPSHOT.TIMESTAMP(History_Context2)</f>
-        <v>invalid object handle 'QSEngine:1:35'; expected QSObject:&lt;type&gt;:&lt;name&gt;:&lt;revision&gt;</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="36" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="7" t="e" cm="1">
+      <c r="B9" s="9" cm="1" t="str">
         <f t="array" ref="B9">_xll.QS.CONTEXT.EVALUATION.DATE(History_Context1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C9" s="7" t="str" cm="1">
+        <v/>
+      </c>
+      <c r="C9" s="9" cm="1" t="str">
         <f t="array" ref="C9">_xll.QS.CONTEXT.EVALUATION.DATE(History_Context2)</f>
-        <v>invalid object handle 'QSEngine:1:35'; expected QSObject:&lt;type&gt;:&lt;name&gt;:&lt;revision&gt;</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="36" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="7" t="str">
+      <c r="B10" s="9">
         <f>History_Rule1</f>
-        <v>Exact</v>
-      </c>
-      <c r="C10" s="7" t="str">
+        <v/>
+      </c>
+      <c r="C10" s="9">
         <f>History_Rule2</f>
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="36" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="11" t="e" cm="1">
+      <c r="B12" s="14" cm="1" t="str">
         <f t="array" ref="B12">_xll.QS.RESULT.VALUE(History_Result1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C12" s="11" t="e" cm="1">
+        <v/>
+      </c>
+      <c r="C12" s="14" cm="1" t="str">
         <f t="array" ref="C12">_xll.QS.RESULT.VALUE(History_Result2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="36" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="11" t="e">
+      <c r="B13" s="14">
         <f>History_PV1-History_PV1</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C13" s="11" t="e">
+        <v/>
+      </c>
+      <c r="C13" s="14">
         <f>History_PV2-History_PV1</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="24" customHeight="1">
+      <c r="A17" s="6" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2802,8 +2691,8 @@
     <mergeCell ref="A2:C3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="A17" location="'1 Inputs'!B18" display="Change timestamp queries →" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="A17" location="'1 Inputs'!B18" display="Change timestamp queries →"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
